--- a/data/PT_Q1_2026_home_name_template.xlsx
+++ b/data/PT_Q1_2026_home_name_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vabs/Documents/GitHub/pt-reporting/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA2A8B38-AC18-BA4F-A085-6D08624BAB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA1E8D9-0E8D-7547-9A51-A20995C5E3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Resident Flow" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="38">
   <si>
     <t>Quarter</t>
   </si>
@@ -152,6 +152,9 @@
   </si>
   <si>
     <t>Group Sessions (per week)</t>
+  </si>
+  <si>
+    <t>Residents Added</t>
   </si>
 </sst>
 </file>
@@ -197,7 +200,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -325,11 +328,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -353,6 +367,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -801,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
@@ -810,10 +830,11 @@
     <col min="5" max="5" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="19.1640625" customWidth="1"/>
+    <col min="8" max="8" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -829,11 +850,14 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
       <c r="G1" s="16"/>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="I1" s="13" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="13"/>
       <c r="B2" s="13"/>
       <c r="C2" s="13"/>
@@ -849,9 +873,10 @@
       <c r="G2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="H2" s="18"/>
+      <c r="I2" s="13"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -874,21 +899,25 @@
         <v>4</v>
       </c>
       <c r="H3" s="3">
+        <v>4</v>
+      </c>
+      <c r="I3" s="3">
         <f>B3+8-(D3+E3)</f>
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="M16" s="1"/>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="H1:H2"/>
+  <mergeCells count="6">
+    <mergeCell ref="I1:I2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:G1"/>
+    <mergeCell ref="H1:H2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/PT_Q1_2026_home_name_template.xlsx
+++ b/data/PT_Q1_2026_home_name_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vabs/Documents/GitHub/pt-reporting/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBA1E8D9-0E8D-7547-9A51-A20995C5E3AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5DD146-ACF9-9D41-BFDC-FB42DA03B64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -896,7 +896,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H3" s="3">
         <v>4</v>
